--- a/artfynd/A 15700-2025 artfynd.xlsx
+++ b/artfynd/A 15700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113166407</v>
+        <v>113166403</v>
       </c>
       <c r="B2" t="n">
-        <v>85632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>236437</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492581</v>
+        <v>492702</v>
       </c>
       <c r="R2" t="n">
-        <v>7029220</v>
+        <v>7029162</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre lågörtsgranskog, nära dike</t>
+          <t>Äldre mossig granskog med lågörtsfläckar, dikeskant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113166408</v>
+        <v>113166402</v>
       </c>
       <c r="B3" t="n">
-        <v>85633</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>236435</v>
+        <v>5754</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Droppklibbskivling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Limacella guttata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) Konrad &amp; Maubl.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492576</v>
+        <v>492703</v>
       </c>
       <c r="R3" t="n">
-        <v>7029193</v>
+        <v>7029157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre lågörtsgranskog, i dikeskant</t>
+          <t>Äldre mossig granskog med lågörtsfläckar, dikeskant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,6 +894,228 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113166408</v>
+      </c>
+      <c r="B4" t="n">
+        <v>89871</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>236435</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Droppklibbskivling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Limacella guttata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers. : Fr.) Konrad &amp; Maubl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kogsta, söder om järnvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>492576</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7029193</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre lågörtsgranskog, i dikeskant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113166407</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89870</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kogsta, söder om järnvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>492581</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7029220</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre lågörtsgranskog, nära dike</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15700-2025 artfynd.xlsx
+++ b/artfynd/A 15700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113166403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113166402</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113166408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113166407</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>